--- a/automation/reports/Excel/Unit_Test_Report.xlsx
+++ b/automation/reports/Excel/Unit_Test_Report.xlsx
@@ -646,7 +646,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         </is>
       </c>
       <c r="E216" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         </is>
       </c>
       <c r="E248" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="F248" s="2" t="inlineStr">
         <is>
@@ -9997,7 +9997,7 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
@@ -12247,7 +12247,7 @@
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         </is>
       </c>
       <c r="E216" s="2" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
@@ -17287,7 +17287,7 @@
         </is>
       </c>
       <c r="E248" s="2" t="n">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="F248" s="2" t="inlineStr">
         <is>
@@ -19119,7 +19119,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-07-26 17:33:55</t>
+          <t>2026-07-26 17:49:50</t>
         </is>
       </c>
     </row>
